--- a/概要/ガントチャート_お茶.xlsx
+++ b/概要/ガントチャート_お茶.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20636573-BB13-4CE1-BF22-1732BFC3DC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C7E436-5740-4412-A85C-D656B949E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1890" yWindow="375" windowWidth="21600" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="62">
   <si>
     <t>AGS2026夏　進捗管理表</t>
     <rPh sb="7" eb="8">
@@ -457,26 +457,6 @@
     <phoneticPr fontId="19"/>
   </si>
   <si>
-    <t>敵の攻撃パターン追加</t>
-    <rPh sb="8" eb="10">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>パリィ成功時拍手SE追加</t>
-    <rPh sb="3" eb="6">
-      <t>セイコウジ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハクシュ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>ImGuiを日本語対応</t>
     <rPh sb="6" eb="9">
       <t>ニホンゴ</t>
@@ -522,6 +502,65 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>バックスタブ時、カメラを背後に設置</t>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイゴ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>カメラ回転機能でプレイヤーが見えるように</t>
+    <rPh sb="3" eb="5">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>当たり判定修正</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>敵の攻撃パターン追加</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>パリィ成功時拍手SE追加</t>
+    <rPh sb="3" eb="5">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハクシュ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -1320,7 +1359,7 @@
     <xf numFmtId="0" fontId="1" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="39" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="39" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1545,6 +1584,34 @@
     <xf numFmtId="0" fontId="20" fillId="42" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1564,39 +1631,36 @@
     <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1655,7 +1719,27 @@
     <cellStyle name="名前" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="良い" xfId="18" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1797,15 +1881,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="作業リスト" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstColumn" dxfId="14"/>
-      <tableStyleElement type="lastColumn" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="secondRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstColumn" dxfId="18"/>
+      <tableStyleElement type="lastColumn" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2161,7 +2245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B4D6C2-4924-46C4-BF7A-0BE92EE1E894}">
-  <dimension ref="A1:CI33"/>
+  <dimension ref="A1:CI40"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32.5546875" style="14" customWidth="1"/>
@@ -2213,224 +2297,224 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="79">
+      <c r="E1" s="87">
         <v>46125</v>
       </c>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="Q1" s="85" t="s">
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="Q1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="AP1" s="85" t="s">
+      <c r="AP1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="AZ1" s="85" t="s">
+      <c r="AZ1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="BT1" s="85" t="s">
+      <c r="BT1" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="CD1" s="88" t="s">
+      <c r="CD1" s="85" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="Q2" s="85"/>
-      <c r="AP2" s="85"/>
-      <c r="AZ2" s="85"/>
-      <c r="BT2" s="85"/>
-      <c r="CD2" s="88"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="Q2" s="83"/>
+      <c r="AP2" s="83"/>
+      <c r="AZ2" s="83"/>
+      <c r="BT2" s="83"/>
+      <c r="CD2" s="85"/>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="Q3" s="85"/>
-      <c r="AP3" s="85"/>
-      <c r="AZ3" s="85"/>
-      <c r="BT3" s="85"/>
-      <c r="CD3" s="88"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="Q3" s="83"/>
+      <c r="AP3" s="83"/>
+      <c r="AZ3" s="83"/>
+      <c r="BT3" s="83"/>
+      <c r="CD3" s="85"/>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="Q4" s="86"/>
-      <c r="AP4" s="86"/>
-      <c r="AZ4" s="86"/>
-      <c r="BT4" s="86"/>
-      <c r="CD4" s="89"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="Q4" s="84"/>
+      <c r="AP4" s="84"/>
+      <c r="AZ4" s="84"/>
+      <c r="BT4" s="84"/>
+      <c r="CD4" s="86"/>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.45">
       <c r="A5" s="70"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="87">
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="82">
         <f>H6</f>
         <v>46125</v>
       </c>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87">
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82">
         <f>H5+7</f>
         <v>46132</v>
       </c>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87">
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82">
         <f>M5+7</f>
         <v>46139</v>
       </c>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87">
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82">
         <f>R5+7</f>
         <v>46146</v>
       </c>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87"/>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87">
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
+      <c r="AB5" s="82">
         <f>W5+7</f>
         <v>46153</v>
       </c>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87">
+      <c r="AC5" s="82"/>
+      <c r="AD5" s="82"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82">
         <f>AB5+7</f>
         <v>46160</v>
       </c>
-      <c r="AH5" s="87"/>
-      <c r="AI5" s="87"/>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="87"/>
-      <c r="AL5" s="87">
+      <c r="AH5" s="82"/>
+      <c r="AI5" s="82"/>
+      <c r="AJ5" s="82"/>
+      <c r="AK5" s="82"/>
+      <c r="AL5" s="82">
         <f>AG5+7</f>
         <v>46167</v>
       </c>
-      <c r="AM5" s="87"/>
-      <c r="AN5" s="87"/>
-      <c r="AO5" s="87"/>
-      <c r="AP5" s="87"/>
-      <c r="AQ5" s="87">
+      <c r="AM5" s="82"/>
+      <c r="AN5" s="82"/>
+      <c r="AO5" s="82"/>
+      <c r="AP5" s="82"/>
+      <c r="AQ5" s="82">
         <f>AL5+7</f>
         <v>46174</v>
       </c>
-      <c r="AR5" s="87"/>
-      <c r="AS5" s="87"/>
-      <c r="AT5" s="87"/>
-      <c r="AU5" s="87"/>
-      <c r="AV5" s="87">
+      <c r="AR5" s="82"/>
+      <c r="AS5" s="82"/>
+      <c r="AT5" s="82"/>
+      <c r="AU5" s="82"/>
+      <c r="AV5" s="82">
         <f>AQ5+7</f>
         <v>46181</v>
       </c>
-      <c r="AW5" s="87"/>
-      <c r="AX5" s="87"/>
-      <c r="AY5" s="87"/>
-      <c r="AZ5" s="87"/>
-      <c r="BA5" s="87">
+      <c r="AW5" s="82"/>
+      <c r="AX5" s="82"/>
+      <c r="AY5" s="82"/>
+      <c r="AZ5" s="82"/>
+      <c r="BA5" s="82">
         <f>AV5+7</f>
         <v>46188</v>
       </c>
-      <c r="BB5" s="87"/>
-      <c r="BC5" s="87"/>
-      <c r="BD5" s="87"/>
-      <c r="BE5" s="87"/>
-      <c r="BF5" s="87">
+      <c r="BB5" s="82"/>
+      <c r="BC5" s="82"/>
+      <c r="BD5" s="82"/>
+      <c r="BE5" s="82"/>
+      <c r="BF5" s="82">
         <f>BA5+7</f>
         <v>46195</v>
       </c>
-      <c r="BG5" s="87"/>
-      <c r="BH5" s="87"/>
-      <c r="BI5" s="87"/>
-      <c r="BJ5" s="87"/>
-      <c r="BK5" s="87">
+      <c r="BG5" s="82"/>
+      <c r="BH5" s="82"/>
+      <c r="BI5" s="82"/>
+      <c r="BJ5" s="82"/>
+      <c r="BK5" s="82">
         <f>BF5+7</f>
         <v>46202</v>
       </c>
-      <c r="BL5" s="87"/>
-      <c r="BM5" s="87"/>
-      <c r="BN5" s="87"/>
-      <c r="BO5" s="87"/>
-      <c r="BP5" s="87">
+      <c r="BL5" s="82"/>
+      <c r="BM5" s="82"/>
+      <c r="BN5" s="82"/>
+      <c r="BO5" s="82"/>
+      <c r="BP5" s="82">
         <f>BK5+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ5" s="87"/>
-      <c r="BR5" s="87"/>
-      <c r="BS5" s="87"/>
-      <c r="BT5" s="87"/>
-      <c r="BU5" s="87">
+      <c r="BQ5" s="82"/>
+      <c r="BR5" s="82"/>
+      <c r="BS5" s="82"/>
+      <c r="BT5" s="82"/>
+      <c r="BU5" s="82">
         <f>BP5+7</f>
         <v>46216</v>
       </c>
-      <c r="BV5" s="87"/>
-      <c r="BW5" s="87"/>
-      <c r="BX5" s="87"/>
-      <c r="BY5" s="87"/>
-      <c r="BZ5" s="87">
+      <c r="BV5" s="82"/>
+      <c r="BW5" s="82"/>
+      <c r="BX5" s="82"/>
+      <c r="BY5" s="82"/>
+      <c r="BZ5" s="82">
         <f>BU5+7</f>
         <v>46223</v>
       </c>
-      <c r="CA5" s="87"/>
-      <c r="CB5" s="87"/>
-      <c r="CC5" s="87"/>
-      <c r="CD5" s="87"/>
-      <c r="CE5" s="87">
+      <c r="CA5" s="82"/>
+      <c r="CB5" s="82"/>
+      <c r="CC5" s="82"/>
+      <c r="CD5" s="82"/>
+      <c r="CE5" s="82">
         <f>BZ5+7</f>
         <v>46230</v>
       </c>
-      <c r="CF5" s="87"/>
-      <c r="CG5" s="87"/>
-      <c r="CH5" s="87"/>
-      <c r="CI5" s="87"/>
+      <c r="CF5" s="82"/>
+      <c r="CG5" s="82"/>
+      <c r="CH5" s="82"/>
+      <c r="CI5" s="82"/>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="66"/>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="91"/>
-      <c r="F6" s="92" t="s">
+      <c r="E6" s="80"/>
+      <c r="F6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="91"/>
+      <c r="G6" s="80"/>
       <c r="H6" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -3322,7 +3406,7 @@
     </row>
     <row r="11" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="62" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>48</v>
@@ -3334,7 +3418,7 @@
         <v>46134</v>
       </c>
       <c r="E11" s="29">
-        <v>46134</v>
+        <v>46138</v>
       </c>
       <c r="F11" s="29">
         <v>46134</v>
@@ -3350,8 +3434,8 @@
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
       <c r="O11" s="77"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
       <c r="R11" s="31"/>
       <c r="S11" s="31"/>
       <c r="T11" s="31"/>
@@ -3425,7 +3509,7 @@
     </row>
     <row r="12" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="62" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>43</v>
@@ -3437,7 +3521,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="29">
-        <v>46135</v>
+        <v>46138</v>
       </c>
       <c r="F12" s="29">
         <v>46134</v>
@@ -3452,7 +3536,7 @@
       <c r="N12" s="31"/>
       <c r="O12" s="77"/>
       <c r="P12" s="77"/>
-      <c r="Q12" s="31"/>
+      <c r="Q12" s="77"/>
       <c r="R12" s="31"/>
       <c r="S12" s="31"/>
       <c r="T12" s="31"/>
@@ -3526,7 +3610,7 @@
     </row>
     <row r="13" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>43</v>
@@ -3536,7 +3620,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="29">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="F13" s="29"/>
       <c r="G13" s="29"/>
@@ -3548,8 +3632,8 @@
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
       <c r="R13" s="31"/>
       <c r="S13" s="31"/>
       <c r="T13" s="31"/>
@@ -3623,7 +3707,7 @@
     </row>
     <row r="14" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="62" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>43</v>
@@ -3633,7 +3717,7 @@
         <v>46135</v>
       </c>
       <c r="E14" s="29">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="F14" s="29"/>
       <c r="G14" s="29"/>
@@ -3645,8 +3729,8 @@
       <c r="M14" s="31"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
       <c r="R14" s="31"/>
       <c r="S14" s="31"/>
       <c r="T14" s="31"/>
@@ -3811,15 +3895,21 @@
     </row>
     <row r="16" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="D16" s="36">
+        <v>46135</v>
+      </c>
+      <c r="E16" s="36">
+        <v>46138</v>
+      </c>
+      <c r="F16" s="36">
+        <v>46135</v>
+      </c>
       <c r="G16" s="36"/>
       <c r="H16" s="37"/>
       <c r="I16" s="38"/>
@@ -3829,8 +3919,8 @@
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
       <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
       <c r="R16" s="38"/>
       <c r="S16" s="38"/>
       <c r="T16" s="38"/>
@@ -3904,16 +3994,24 @@
     </row>
     <row r="17" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="63" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B17" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
+      <c r="D17" s="42">
+        <v>46135</v>
+      </c>
+      <c r="E17" s="42">
+        <v>46138</v>
+      </c>
+      <c r="F17" s="42">
+        <v>46135</v>
+      </c>
+      <c r="G17" s="42">
+        <v>46135</v>
+      </c>
       <c r="H17" s="43"/>
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
@@ -3922,8 +4020,8 @@
       <c r="M17" s="44"/>
       <c r="N17" s="44"/>
       <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="44"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
       <c r="R17" s="44"/>
       <c r="S17" s="44"/>
       <c r="T17" s="44"/>
@@ -3997,16 +4095,24 @@
     </row>
     <row r="18" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="63" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
+      <c r="D18" s="42">
+        <v>46135</v>
+      </c>
+      <c r="E18" s="42">
+        <v>46138</v>
+      </c>
+      <c r="F18" s="42">
+        <v>46135</v>
+      </c>
+      <c r="G18" s="42">
+        <v>46135</v>
+      </c>
       <c r="H18" s="43"/>
       <c r="I18" s="44"/>
       <c r="J18" s="44"/>
@@ -4015,8 +4121,8 @@
       <c r="M18" s="44"/>
       <c r="N18" s="44"/>
       <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="77"/>
       <c r="R18" s="44"/>
       <c r="S18" s="44"/>
       <c r="T18" s="44"/>
@@ -4090,14 +4196,18 @@
     </row>
     <row r="19" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="63" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B19" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
+      <c r="D19" s="42">
+        <v>46135</v>
+      </c>
+      <c r="E19" s="42">
+        <v>46138</v>
+      </c>
       <c r="F19" s="42"/>
       <c r="G19" s="42"/>
       <c r="H19" s="43"/>
@@ -4108,8 +4218,8 @@
       <c r="M19" s="44"/>
       <c r="N19" s="44"/>
       <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="77"/>
       <c r="R19" s="44"/>
       <c r="S19" s="44"/>
       <c r="T19" s="44"/>
@@ -4365,15 +4475,21 @@
     </row>
     <row r="22" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="48"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
+      <c r="D22" s="49">
+        <v>46135</v>
+      </c>
+      <c r="E22" s="49">
+        <v>46138</v>
+      </c>
+      <c r="F22" s="49">
+        <v>46135</v>
+      </c>
       <c r="G22" s="49"/>
       <c r="H22" s="50"/>
       <c r="I22" s="51"/>
@@ -4457,14 +4573,22 @@
       <c r="CI22" s="51"/>
     </row>
     <row r="23" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="64"/>
+      <c r="A23" s="64" t="s">
+        <v>52</v>
+      </c>
       <c r="B23" s="53" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="54"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
+      <c r="D23" s="55">
+        <v>46135</v>
+      </c>
+      <c r="E23" s="55">
+        <v>46138</v>
+      </c>
+      <c r="F23" s="55">
+        <v>46135</v>
+      </c>
       <c r="G23" s="55"/>
       <c r="H23" s="56"/>
       <c r="I23" s="57"/>
@@ -4548,14 +4672,22 @@
       <c r="CI23" s="57"/>
     </row>
     <row r="24" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="64"/>
+      <c r="A24" s="64" t="s">
+        <v>60</v>
+      </c>
       <c r="B24" s="53" t="s">
         <v>48</v>
       </c>
       <c r="C24" s="54"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
+      <c r="D24" s="55">
+        <v>46135</v>
+      </c>
+      <c r="E24" s="55">
+        <v>46138</v>
+      </c>
+      <c r="F24" s="55">
+        <v>46135</v>
+      </c>
       <c r="G24" s="55"/>
       <c r="H24" s="56"/>
       <c r="I24" s="57"/>
@@ -4639,14 +4771,22 @@
       <c r="CI24" s="57"/>
     </row>
     <row r="25" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="64"/>
+      <c r="A25" s="64" t="s">
+        <v>61</v>
+      </c>
       <c r="B25" s="53" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="54"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
+      <c r="D25" s="55">
+        <v>46135</v>
+      </c>
+      <c r="E25" s="55">
+        <v>46138</v>
+      </c>
+      <c r="F25" s="55">
+        <v>46135</v>
+      </c>
       <c r="G25" s="55"/>
       <c r="H25" s="56"/>
       <c r="I25" s="57"/>
@@ -5004,12 +5144,116 @@
       <c r="CI29" s="60"/>
     </row>
     <row r="30" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="31" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="32" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="31" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="97"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="95"/>
+    </row>
+    <row r="32" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="101"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="99"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="95"/>
+    </row>
+    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="101"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="95"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="101"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="95"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="98"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="95"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="97"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="99"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="95"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="101"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="95"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="101"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="95"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="101"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="98"/>
+      <c r="G39" s="95"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="95"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="96"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+    </row>
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="30">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="Q1:Q4"/>
+    <mergeCell ref="CE5:CI5"/>
+    <mergeCell ref="BP5:BT5"/>
+    <mergeCell ref="BU5:BY5"/>
+    <mergeCell ref="BZ5:CD5"/>
+    <mergeCell ref="AP1:AP4"/>
+    <mergeCell ref="AZ1:AZ4"/>
+    <mergeCell ref="BT1:BT4"/>
+    <mergeCell ref="CD1:CD4"/>
+    <mergeCell ref="R5:V5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="BA5:BE5"/>
@@ -5023,38 +5267,36 @@
     <mergeCell ref="AV5:AZ5"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Q1:Q4"/>
-    <mergeCell ref="CE5:CI5"/>
-    <mergeCell ref="BP5:BT5"/>
-    <mergeCell ref="BU5:BY5"/>
-    <mergeCell ref="BZ5:CD5"/>
-    <mergeCell ref="AP1:AP4"/>
-    <mergeCell ref="AZ1:AZ4"/>
-    <mergeCell ref="BT1:BT4"/>
-    <mergeCell ref="CD1:CD4"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
-  <conditionalFormatting sqref="F10:G10 F14:G27 G13">
-    <cfRule type="expression" dxfId="8" priority="5">
+  <conditionalFormatting sqref="F10:G10 F14:G21 G13 G22 F23:G27">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>D10&lt;F10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>E8&lt;G8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>D8&lt;F8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:D25">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>B23&lt;D23</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:F34">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>D32&lt;F32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D32:D34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B32&lt;D32</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.27559055118110237" top="0.35433070866141736" bottom="0.23622047244094491" header="0.31496062992125984" footer="0.11811023622047245"/>
@@ -5118,44 +5360,44 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="79">
+      <c r="E1" s="87">
         <v>46125</v>
       </c>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D5" s="93"/>
@@ -5165,161 +5407,161 @@
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="70"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="87">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="82">
         <f>H7</f>
         <v>46125</v>
       </c>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87">
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82">
         <f>H6+7</f>
         <v>46132</v>
       </c>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="87"/>
-      <c r="R6" s="87">
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82">
         <f>M6+7</f>
         <v>46139</v>
       </c>
-      <c r="S6" s="87"/>
-      <c r="T6" s="87"/>
-      <c r="U6" s="87"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="87">
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82">
         <f>R6+7</f>
         <v>46146</v>
       </c>
-      <c r="X6" s="87"/>
-      <c r="Y6" s="87"/>
-      <c r="Z6" s="87"/>
-      <c r="AA6" s="87"/>
-      <c r="AB6" s="87">
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82">
         <f>W6+7</f>
         <v>46153</v>
       </c>
-      <c r="AC6" s="87"/>
-      <c r="AD6" s="87"/>
-      <c r="AE6" s="87"/>
-      <c r="AF6" s="87"/>
-      <c r="AG6" s="87">
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="82">
         <f>AB6+7</f>
         <v>46160</v>
       </c>
-      <c r="AH6" s="87"/>
-      <c r="AI6" s="87"/>
-      <c r="AJ6" s="87"/>
-      <c r="AK6" s="87"/>
-      <c r="AL6" s="87">
+      <c r="AH6" s="82"/>
+      <c r="AI6" s="82"/>
+      <c r="AJ6" s="82"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="82">
         <f>AG6+7</f>
         <v>46167</v>
       </c>
-      <c r="AM6" s="87"/>
-      <c r="AN6" s="87"/>
-      <c r="AO6" s="87"/>
-      <c r="AP6" s="87"/>
-      <c r="AQ6" s="87">
+      <c r="AM6" s="82"/>
+      <c r="AN6" s="82"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="82"/>
+      <c r="AQ6" s="82">
         <f>AL6+7</f>
         <v>46174</v>
       </c>
-      <c r="AR6" s="87"/>
-      <c r="AS6" s="87"/>
-      <c r="AT6" s="87"/>
-      <c r="AU6" s="87"/>
-      <c r="AV6" s="87">
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="82"/>
+      <c r="AU6" s="82"/>
+      <c r="AV6" s="82">
         <f>AQ6+7</f>
         <v>46181</v>
       </c>
-      <c r="AW6" s="87"/>
-      <c r="AX6" s="87"/>
-      <c r="AY6" s="87"/>
-      <c r="AZ6" s="87"/>
-      <c r="BA6" s="87">
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="82"/>
+      <c r="AY6" s="82"/>
+      <c r="AZ6" s="82"/>
+      <c r="BA6" s="82">
         <f>AV6+7</f>
         <v>46188</v>
       </c>
-      <c r="BB6" s="87"/>
-      <c r="BC6" s="87"/>
-      <c r="BD6" s="87"/>
-      <c r="BE6" s="87"/>
-      <c r="BF6" s="87">
+      <c r="BB6" s="82"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="82"/>
+      <c r="BE6" s="82"/>
+      <c r="BF6" s="82">
         <f>BA6+7</f>
         <v>46195</v>
       </c>
-      <c r="BG6" s="87"/>
-      <c r="BH6" s="87"/>
-      <c r="BI6" s="87"/>
-      <c r="BJ6" s="87"/>
-      <c r="BK6" s="87">
+      <c r="BG6" s="82"/>
+      <c r="BH6" s="82"/>
+      <c r="BI6" s="82"/>
+      <c r="BJ6" s="82"/>
+      <c r="BK6" s="82">
         <f>BF6+7</f>
         <v>46202</v>
       </c>
-      <c r="BL6" s="87"/>
-      <c r="BM6" s="87"/>
-      <c r="BN6" s="87"/>
-      <c r="BO6" s="87"/>
-      <c r="BP6" s="87">
+      <c r="BL6" s="82"/>
+      <c r="BM6" s="82"/>
+      <c r="BN6" s="82"/>
+      <c r="BO6" s="82"/>
+      <c r="BP6" s="82">
         <f>BK6+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ6" s="87"/>
-      <c r="BR6" s="87"/>
-      <c r="BS6" s="87"/>
-      <c r="BT6" s="87"/>
-      <c r="BU6" s="87">
+      <c r="BQ6" s="82"/>
+      <c r="BR6" s="82"/>
+      <c r="BS6" s="82"/>
+      <c r="BT6" s="82"/>
+      <c r="BU6" s="82">
         <f>BP6+7</f>
         <v>46216</v>
       </c>
-      <c r="BV6" s="87"/>
-      <c r="BW6" s="87"/>
-      <c r="BX6" s="87"/>
-      <c r="BY6" s="87"/>
-      <c r="BZ6" s="87">
+      <c r="BV6" s="82"/>
+      <c r="BW6" s="82"/>
+      <c r="BX6" s="82"/>
+      <c r="BY6" s="82"/>
+      <c r="BZ6" s="82">
         <f>BU6+7</f>
         <v>46223</v>
       </c>
-      <c r="CA6" s="87"/>
-      <c r="CB6" s="87"/>
-      <c r="CC6" s="87"/>
-      <c r="CD6" s="87"/>
-      <c r="CE6" s="87">
+      <c r="CA6" s="82"/>
+      <c r="CB6" s="82"/>
+      <c r="CC6" s="82"/>
+      <c r="CD6" s="82"/>
+      <c r="CE6" s="82">
         <f>BZ6+7</f>
         <v>46230</v>
       </c>
-      <c r="CF6" s="87"/>
-      <c r="CG6" s="87"/>
-      <c r="CH6" s="87"/>
-      <c r="CI6" s="87"/>
-      <c r="CJ6" s="87">
+      <c r="CF6" s="82"/>
+      <c r="CG6" s="82"/>
+      <c r="CH6" s="82"/>
+      <c r="CI6" s="82"/>
+      <c r="CJ6" s="82">
         <f>CE6+7</f>
         <v>46237</v>
       </c>
-      <c r="CK6" s="87"/>
-      <c r="CL6" s="87"/>
-      <c r="CM6" s="87"/>
-      <c r="CN6" s="87"/>
+      <c r="CK6" s="82"/>
+      <c r="CL6" s="82"/>
+      <c r="CM6" s="82"/>
+      <c r="CN6" s="82"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="65"/>
       <c r="B7" s="65"/>
       <c r="C7" s="66"/>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="92" t="s">
+      <c r="E7" s="80"/>
+      <c r="F7" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="91"/>
+      <c r="G7" s="80"/>
       <c r="H7" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -8403,18 +8645,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -8431,35 +8661,47 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F15:G32">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>D15&lt;F15</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>E9&lt;G9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>D9&lt;F9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G11 G13:G14">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>E10&lt;G10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F14">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>D10&lt;F10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>E12&lt;G12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8469,6 +8711,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C2961D859B1A8B4697EC07BF3C3DAD3B" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ab0ad3b8596db009aba937b3e43a8a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="02709b60-37ec-424b-b681-c6612ac7fe32" xmlns:ns3="f9048785-d070-4c78-8f2f-ed2b48eb345c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd157c9246152f7d64d090db49938ccd" ns2:_="" ns3:_="">
     <xsd:import namespace="02709b60-37ec-424b-b681-c6612ac7fe32"/>
@@ -8703,34 +8972,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
+    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60750451-81D0-4123-9068-1385884A2A7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8747,23 +9008,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
-    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/概要/ガントチャート_お茶.xlsx
+++ b/概要/ガントチャート_お茶.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C7E436-5740-4412-A85C-D656B949E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B130C109-CBF5-44EE-86A3-8EF5C1474711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="375" windowWidth="21600" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="735" windowWidth="21600" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進捗確認表" sheetId="19" r:id="rId1"/>
@@ -1584,16 +1584,48 @@
     <xf numFmtId="0" fontId="20" fillId="42" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1604,6 +1636,9 @@
       <alignment horizontal="center" textRotation="255"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" textRotation="255"/>
       <protection locked="0"/>
@@ -1612,23 +1647,13 @@
       <alignment horizontal="center" textRotation="255"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="17" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1636,31 +1661,6 @@
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1719,12 +1719,7 @@
     <cellStyle name="名前" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="良い" xfId="18" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1881,15 +1876,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="作業リスト" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstColumn" dxfId="18"/>
-      <tableStyleElement type="lastColumn" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" dxfId="20"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="totalRow" dxfId="18"/>
+      <tableStyleElement type="firstColumn" dxfId="17"/>
+      <tableStyleElement type="lastColumn" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2297,224 +2292,224 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="87">
+      <c r="E1" s="86">
         <v>46125</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="Q1" s="83" t="s">
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="Q1" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="AP1" s="83" t="s">
+      <c r="AP1" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="AZ1" s="83" t="s">
+      <c r="AZ1" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="BT1" s="83" t="s">
+      <c r="BT1" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="CD1" s="85" t="s">
+      <c r="CD1" s="95" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="Q2" s="83"/>
-      <c r="AP2" s="83"/>
-      <c r="AZ2" s="83"/>
-      <c r="BT2" s="83"/>
-      <c r="CD2" s="85"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="Q2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AZ2" s="92"/>
+      <c r="BT2" s="92"/>
+      <c r="CD2" s="95"/>
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="Q3" s="83"/>
-      <c r="AP3" s="83"/>
-      <c r="AZ3" s="83"/>
-      <c r="BT3" s="83"/>
-      <c r="CD3" s="85"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="Q3" s="92"/>
+      <c r="AP3" s="92"/>
+      <c r="AZ3" s="92"/>
+      <c r="BT3" s="92"/>
+      <c r="CD3" s="95"/>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.45">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="Q4" s="84"/>
-      <c r="AP4" s="84"/>
-      <c r="AZ4" s="84"/>
-      <c r="BT4" s="84"/>
-      <c r="CD4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="Q4" s="93"/>
+      <c r="AP4" s="93"/>
+      <c r="AZ4" s="93"/>
+      <c r="BT4" s="93"/>
+      <c r="CD4" s="96"/>
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.45">
       <c r="A5" s="70"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="82">
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="94">
         <f>H6</f>
         <v>46125</v>
       </c>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82">
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94">
         <f>H5+7</f>
         <v>46132</v>
       </c>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82">
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94">
         <f>M5+7</f>
         <v>46139</v>
       </c>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82">
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
+      <c r="W5" s="94">
         <f>R5+7</f>
         <v>46146</v>
       </c>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82">
+      <c r="X5" s="94"/>
+      <c r="Y5" s="94"/>
+      <c r="Z5" s="94"/>
+      <c r="AA5" s="94"/>
+      <c r="AB5" s="94">
         <f>W5+7</f>
         <v>46153</v>
       </c>
-      <c r="AC5" s="82"/>
-      <c r="AD5" s="82"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="82"/>
-      <c r="AG5" s="82">
+      <c r="AC5" s="94"/>
+      <c r="AD5" s="94"/>
+      <c r="AE5" s="94"/>
+      <c r="AF5" s="94"/>
+      <c r="AG5" s="94">
         <f>AB5+7</f>
         <v>46160</v>
       </c>
-      <c r="AH5" s="82"/>
-      <c r="AI5" s="82"/>
-      <c r="AJ5" s="82"/>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82">
+      <c r="AH5" s="94"/>
+      <c r="AI5" s="94"/>
+      <c r="AJ5" s="94"/>
+      <c r="AK5" s="94"/>
+      <c r="AL5" s="94">
         <f>AG5+7</f>
         <v>46167</v>
       </c>
-      <c r="AM5" s="82"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="82"/>
-      <c r="AQ5" s="82">
+      <c r="AM5" s="94"/>
+      <c r="AN5" s="94"/>
+      <c r="AO5" s="94"/>
+      <c r="AP5" s="94"/>
+      <c r="AQ5" s="94">
         <f>AL5+7</f>
         <v>46174</v>
       </c>
-      <c r="AR5" s="82"/>
-      <c r="AS5" s="82"/>
-      <c r="AT5" s="82"/>
-      <c r="AU5" s="82"/>
-      <c r="AV5" s="82">
+      <c r="AR5" s="94"/>
+      <c r="AS5" s="94"/>
+      <c r="AT5" s="94"/>
+      <c r="AU5" s="94"/>
+      <c r="AV5" s="94">
         <f>AQ5+7</f>
         <v>46181</v>
       </c>
-      <c r="AW5" s="82"/>
-      <c r="AX5" s="82"/>
-      <c r="AY5" s="82"/>
-      <c r="AZ5" s="82"/>
-      <c r="BA5" s="82">
+      <c r="AW5" s="94"/>
+      <c r="AX5" s="94"/>
+      <c r="AY5" s="94"/>
+      <c r="AZ5" s="94"/>
+      <c r="BA5" s="94">
         <f>AV5+7</f>
         <v>46188</v>
       </c>
-      <c r="BB5" s="82"/>
-      <c r="BC5" s="82"/>
-      <c r="BD5" s="82"/>
-      <c r="BE5" s="82"/>
-      <c r="BF5" s="82">
+      <c r="BB5" s="94"/>
+      <c r="BC5" s="94"/>
+      <c r="BD5" s="94"/>
+      <c r="BE5" s="94"/>
+      <c r="BF5" s="94">
         <f>BA5+7</f>
         <v>46195</v>
       </c>
-      <c r="BG5" s="82"/>
-      <c r="BH5" s="82"/>
-      <c r="BI5" s="82"/>
-      <c r="BJ5" s="82"/>
-      <c r="BK5" s="82">
+      <c r="BG5" s="94"/>
+      <c r="BH5" s="94"/>
+      <c r="BI5" s="94"/>
+      <c r="BJ5" s="94"/>
+      <c r="BK5" s="94">
         <f>BF5+7</f>
         <v>46202</v>
       </c>
-      <c r="BL5" s="82"/>
-      <c r="BM5" s="82"/>
-      <c r="BN5" s="82"/>
-      <c r="BO5" s="82"/>
-      <c r="BP5" s="82">
+      <c r="BL5" s="94"/>
+      <c r="BM5" s="94"/>
+      <c r="BN5" s="94"/>
+      <c r="BO5" s="94"/>
+      <c r="BP5" s="94">
         <f>BK5+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ5" s="82"/>
-      <c r="BR5" s="82"/>
-      <c r="BS5" s="82"/>
-      <c r="BT5" s="82"/>
-      <c r="BU5" s="82">
+      <c r="BQ5" s="94"/>
+      <c r="BR5" s="94"/>
+      <c r="BS5" s="94"/>
+      <c r="BT5" s="94"/>
+      <c r="BU5" s="94">
         <f>BP5+7</f>
         <v>46216</v>
       </c>
-      <c r="BV5" s="82"/>
-      <c r="BW5" s="82"/>
-      <c r="BX5" s="82"/>
-      <c r="BY5" s="82"/>
-      <c r="BZ5" s="82">
+      <c r="BV5" s="94"/>
+      <c r="BW5" s="94"/>
+      <c r="BX5" s="94"/>
+      <c r="BY5" s="94"/>
+      <c r="BZ5" s="94">
         <f>BU5+7</f>
         <v>46223</v>
       </c>
-      <c r="CA5" s="82"/>
-      <c r="CB5" s="82"/>
-      <c r="CC5" s="82"/>
-      <c r="CD5" s="82"/>
-      <c r="CE5" s="82">
+      <c r="CA5" s="94"/>
+      <c r="CB5" s="94"/>
+      <c r="CC5" s="94"/>
+      <c r="CD5" s="94"/>
+      <c r="CE5" s="94">
         <f>BZ5+7</f>
         <v>46230</v>
       </c>
-      <c r="CF5" s="82"/>
-      <c r="CG5" s="82"/>
-      <c r="CH5" s="82"/>
-      <c r="CI5" s="82"/>
+      <c r="CF5" s="94"/>
+      <c r="CG5" s="94"/>
+      <c r="CH5" s="94"/>
+      <c r="CI5" s="94"/>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="66"/>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="81" t="s">
+      <c r="E6" s="98"/>
+      <c r="F6" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="80"/>
+      <c r="G6" s="98"/>
       <c r="H6" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -5145,115 +5140,98 @@
     </row>
     <row r="30" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="97"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="95"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="79"/>
     </row>
     <row r="32" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="101"/>
-      <c r="B32" s="98"/>
-      <c r="C32" s="99"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="95"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="82"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="79"/>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="101"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="99"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="95"/>
+      <c r="A33" s="85"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="79"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="101"/>
-      <c r="B34" s="98"/>
-      <c r="C34" s="99"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="95"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="79"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="98"/>
-      <c r="B35" s="98"/>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="95"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="79"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="97"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="99"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="99"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="95"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="79"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="101"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="95"/>
+      <c r="A37" s="85"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="79"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="101"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="99"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="95"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="79"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="101"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="99"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="98"/>
-      <c r="G39" s="95"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="79"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="95"/>
-      <c r="B40" s="95"/>
-      <c r="C40" s="96"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="96"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
+      <c r="A40" s="79"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
     </row>
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="30">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="Q1:Q4"/>
-    <mergeCell ref="CE5:CI5"/>
-    <mergeCell ref="BP5:BT5"/>
-    <mergeCell ref="BU5:BY5"/>
-    <mergeCell ref="BZ5:CD5"/>
-    <mergeCell ref="AP1:AP4"/>
-    <mergeCell ref="AZ1:AZ4"/>
-    <mergeCell ref="BT1:BT4"/>
-    <mergeCell ref="CD1:CD4"/>
-    <mergeCell ref="R5:V5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="BA5:BE5"/>
@@ -5267,35 +5245,52 @@
     <mergeCell ref="AV5:AZ5"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Q1:Q4"/>
+    <mergeCell ref="CE5:CI5"/>
+    <mergeCell ref="BP5:BT5"/>
+    <mergeCell ref="BU5:BY5"/>
+    <mergeCell ref="BZ5:CD5"/>
+    <mergeCell ref="AP1:AP4"/>
+    <mergeCell ref="AZ1:AZ4"/>
+    <mergeCell ref="BT1:BT4"/>
+    <mergeCell ref="CD1:CD4"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F10:G10 F14:G21 G13 G22 F23:G27">
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>D10&lt;F10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>E8&lt;G8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>D8&lt;F8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:D25">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>B23&lt;D23</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>D32&lt;F32</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32:D34">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>B32&lt;D32</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5360,208 +5355,208 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="87">
+      <c r="E1" s="86">
         <v>46125</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="70"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="82">
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="94">
         <f>H7</f>
         <v>46125</v>
       </c>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82">
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94">
         <f>H6+7</f>
         <v>46132</v>
       </c>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82"/>
-      <c r="Q6" s="82"/>
-      <c r="R6" s="82">
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94">
         <f>M6+7</f>
         <v>46139</v>
       </c>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="82"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="82">
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="94">
         <f>R6+7</f>
         <v>46146</v>
       </c>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="82"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="82">
+      <c r="X6" s="94"/>
+      <c r="Y6" s="94"/>
+      <c r="Z6" s="94"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="94">
         <f>W6+7</f>
         <v>46153</v>
       </c>
-      <c r="AC6" s="82"/>
-      <c r="AD6" s="82"/>
-      <c r="AE6" s="82"/>
-      <c r="AF6" s="82"/>
-      <c r="AG6" s="82">
+      <c r="AC6" s="94"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="94"/>
+      <c r="AF6" s="94"/>
+      <c r="AG6" s="94">
         <f>AB6+7</f>
         <v>46160</v>
       </c>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="82"/>
-      <c r="AJ6" s="82"/>
-      <c r="AK6" s="82"/>
-      <c r="AL6" s="82">
+      <c r="AH6" s="94"/>
+      <c r="AI6" s="94"/>
+      <c r="AJ6" s="94"/>
+      <c r="AK6" s="94"/>
+      <c r="AL6" s="94">
         <f>AG6+7</f>
         <v>46167</v>
       </c>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
-      <c r="AO6" s="82"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="82">
+      <c r="AM6" s="94"/>
+      <c r="AN6" s="94"/>
+      <c r="AO6" s="94"/>
+      <c r="AP6" s="94"/>
+      <c r="AQ6" s="94">
         <f>AL6+7</f>
         <v>46174</v>
       </c>
-      <c r="AR6" s="82"/>
-      <c r="AS6" s="82"/>
-      <c r="AT6" s="82"/>
-      <c r="AU6" s="82"/>
-      <c r="AV6" s="82">
+      <c r="AR6" s="94"/>
+      <c r="AS6" s="94"/>
+      <c r="AT6" s="94"/>
+      <c r="AU6" s="94"/>
+      <c r="AV6" s="94">
         <f>AQ6+7</f>
         <v>46181</v>
       </c>
-      <c r="AW6" s="82"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="82"/>
-      <c r="AZ6" s="82"/>
-      <c r="BA6" s="82">
+      <c r="AW6" s="94"/>
+      <c r="AX6" s="94"/>
+      <c r="AY6" s="94"/>
+      <c r="AZ6" s="94"/>
+      <c r="BA6" s="94">
         <f>AV6+7</f>
         <v>46188</v>
       </c>
-      <c r="BB6" s="82"/>
-      <c r="BC6" s="82"/>
-      <c r="BD6" s="82"/>
-      <c r="BE6" s="82"/>
-      <c r="BF6" s="82">
+      <c r="BB6" s="94"/>
+      <c r="BC6" s="94"/>
+      <c r="BD6" s="94"/>
+      <c r="BE6" s="94"/>
+      <c r="BF6" s="94">
         <f>BA6+7</f>
         <v>46195</v>
       </c>
-      <c r="BG6" s="82"/>
-      <c r="BH6" s="82"/>
-      <c r="BI6" s="82"/>
-      <c r="BJ6" s="82"/>
-      <c r="BK6" s="82">
+      <c r="BG6" s="94"/>
+      <c r="BH6" s="94"/>
+      <c r="BI6" s="94"/>
+      <c r="BJ6" s="94"/>
+      <c r="BK6" s="94">
         <f>BF6+7</f>
         <v>46202</v>
       </c>
-      <c r="BL6" s="82"/>
-      <c r="BM6" s="82"/>
-      <c r="BN6" s="82"/>
-      <c r="BO6" s="82"/>
-      <c r="BP6" s="82">
+      <c r="BL6" s="94"/>
+      <c r="BM6" s="94"/>
+      <c r="BN6" s="94"/>
+      <c r="BO6" s="94"/>
+      <c r="BP6" s="94">
         <f>BK6+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ6" s="82"/>
-      <c r="BR6" s="82"/>
-      <c r="BS6" s="82"/>
-      <c r="BT6" s="82"/>
-      <c r="BU6" s="82">
+      <c r="BQ6" s="94"/>
+      <c r="BR6" s="94"/>
+      <c r="BS6" s="94"/>
+      <c r="BT6" s="94"/>
+      <c r="BU6" s="94">
         <f>BP6+7</f>
         <v>46216</v>
       </c>
-      <c r="BV6" s="82"/>
-      <c r="BW6" s="82"/>
-      <c r="BX6" s="82"/>
-      <c r="BY6" s="82"/>
-      <c r="BZ6" s="82">
+      <c r="BV6" s="94"/>
+      <c r="BW6" s="94"/>
+      <c r="BX6" s="94"/>
+      <c r="BY6" s="94"/>
+      <c r="BZ6" s="94">
         <f>BU6+7</f>
         <v>46223</v>
       </c>
-      <c r="CA6" s="82"/>
-      <c r="CB6" s="82"/>
-      <c r="CC6" s="82"/>
-      <c r="CD6" s="82"/>
-      <c r="CE6" s="82">
+      <c r="CA6" s="94"/>
+      <c r="CB6" s="94"/>
+      <c r="CC6" s="94"/>
+      <c r="CD6" s="94"/>
+      <c r="CE6" s="94">
         <f>BZ6+7</f>
         <v>46230</v>
       </c>
-      <c r="CF6" s="82"/>
-      <c r="CG6" s="82"/>
-      <c r="CH6" s="82"/>
-      <c r="CI6" s="82"/>
-      <c r="CJ6" s="82">
+      <c r="CF6" s="94"/>
+      <c r="CG6" s="94"/>
+      <c r="CH6" s="94"/>
+      <c r="CI6" s="94"/>
+      <c r="CJ6" s="94">
         <f>CE6+7</f>
         <v>46237</v>
       </c>
-      <c r="CK6" s="82"/>
-      <c r="CL6" s="82"/>
-      <c r="CM6" s="82"/>
-      <c r="CN6" s="82"/>
+      <c r="CK6" s="94"/>
+      <c r="CL6" s="94"/>
+      <c r="CM6" s="94"/>
+      <c r="CN6" s="94"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="65"/>
       <c r="B7" s="65"/>
       <c r="C7" s="66"/>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81" t="s">
+      <c r="E7" s="98"/>
+      <c r="F7" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="80"/>
+      <c r="G7" s="98"/>
       <c r="H7" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -8645,6 +8640,18 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -8661,47 +8668,35 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F15:G32">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>D15&lt;F15</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>E9&lt;G9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>D9&lt;F9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G11 G13:G14">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>E10&lt;G10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F14">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>D10&lt;F10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>E12&lt;G12</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8711,33 +8706,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C2961D859B1A8B4697EC07BF3C3DAD3B" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ab0ad3b8596db009aba937b3e43a8a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="02709b60-37ec-424b-b681-c6612ac7fe32" xmlns:ns3="f9048785-d070-4c78-8f2f-ed2b48eb345c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd157c9246152f7d64d090db49938ccd" ns2:_="" ns3:_="">
     <xsd:import namespace="02709b60-37ec-424b-b681-c6612ac7fe32"/>
@@ -8972,26 +8940,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
-    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60750451-81D0-4123-9068-1385884A2A7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9008,4 +8984,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
+    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>